--- a/templates/CBX250_Model_Assumptions_Template.xlsx
+++ b/templates/CBX250_Model_Assumptions_Template.xlsx
@@ -9,13 +9,14 @@
     <sheet name="Scenario_Controls" sheetId="2" r:id="rId2"/>
     <sheet name="Launch_Timing" sheetId="3" r:id="rId3"/>
     <sheet name="Dosing_Assumptions" sheetId="4" r:id="rId4"/>
-    <sheet name="Product_Parameters" sheetId="5" r:id="rId5"/>
-    <sheet name="Yield_Assumptions" sheetId="6" r:id="rId6"/>
-    <sheet name="Packaging_and_Vialing" sheetId="7" r:id="rId7"/>
-    <sheet name="SS_Assumptions" sheetId="8" r:id="rId8"/>
-    <sheet name="CML_Prevalent_Assumptions" sheetId="9" r:id="rId9"/>
-    <sheet name="Trade_Inventory_FutureHooks" sheetId="10" r:id="rId10"/>
-    <sheet name="Lookup_Lists" sheetId="11" r:id="rId11"/>
+    <sheet name="Treatment_Duration_Assumptions" sheetId="5" r:id="rId5"/>
+    <sheet name="Product_Parameters" sheetId="6" r:id="rId6"/>
+    <sheet name="Yield_Assumptions" sheetId="7" r:id="rId7"/>
+    <sheet name="Packaging_and_Vialing" sheetId="8" r:id="rId8"/>
+    <sheet name="SS_Assumptions" sheetId="9" r:id="rId9"/>
+    <sheet name="CML_Prevalent_Assumptions" sheetId="10" r:id="rId10"/>
+    <sheet name="Trade_Inventory_FutureHooks" sheetId="11" r:id="rId11"/>
+    <sheet name="Lookup_Lists" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,7 +132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -203,90 +204,107 @@
       </c>
       <c r="C4" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">One active Scenario_Controls row is required. Dosing_Assumptions should provide one active module row for AML, MDS, CML_Incident, and CML_Prevalent.</t>
+          <t xml:space="preserve">One active Scenario_Controls row is required. Dosing_Assumptions should provide one active module row for AML, MDS, CML_Incident, and CML_Prevalent. The seeded base case uses demand_basis = patient_starts, so populate active Treatment_Duration_Assumptions rows before running the forecast workflow.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="4">
         <is>
-          <t xml:space="preserve">Scope precedence</t>
+          <t xml:space="preserve">Phase 1 demand basis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">When a sheet supports both scenario-level defaults and module-specific overrides, module-specific override rows take precedence over scenario-default rows.</t>
+          <t xml:space="preserve">patient_starts is the preferred default operating mode and represents the approved base-case commercial input path.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current generated Phase 2 config already applies this precedence for module FG mg per unit. For ds_qty_per_dp_unit_mg and ds_overage_factor, module overrides are preserved in normalized artifacts but the current engine still consumes the scenario default only.</t>
+          <t xml:space="preserve">treated_census remains supported for backward compatibility and special cases only. Do not apply duration logic on top of already treated-census inputs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="4">
         <is>
-          <t xml:space="preserve">Current engine wiring</t>
+          <t xml:space="preserve">Scope precedence</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml and generated_phase2_scenario.toml.</t>
+          <t xml:space="preserve">When a sheet supports both scenario-level defaults and module-specific overrides, module-specific override rows take precedence over scenario-default rows.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current Phase 2 wiring consumes: dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode.</t>
+          <t xml:space="preserve">Current generated Phase 2 config already applies this precedence for module FG mg per unit. For ds_qty_per_dp_unit_mg and ds_overage_factor, module overrides are preserved in normalized artifacts but the current engine still consumes the scenario default only.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="4">
         <is>
-          <t xml:space="preserve">Future-ready fields</t>
+          <t xml:space="preserve">Current engine wiring</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Launch_Timing, geography-specific overrides, segment-specific overrides, dp_concentration_mg_per_ml, dp_fill_volume_ml, and Trade_Inventory_FutureHooks are preserved in normalized outputs even if not yet wired into active model logic.</t>
+          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml and generated_phase2_scenario.toml.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic.</t>
+          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode, and dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="4">
         <is>
-          <t xml:space="preserve">Workbook to model bridge</t>
+          <t xml:space="preserve">Future-ready fields</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">After import, use the generated Phase 2 scenario directly or pass it into the one-command forecast workflow as --phase2-scenario.</t>
+          <t xml:space="preserve">Launch_Timing, geography-specific overrides, segment-specific overrides, dp_concentration_mg_per_ml, dp_fill_volume_ml, and Trade_Inventory_FutureHooks are preserved in normalized outputs even if not yet wired into active model logic.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions.</t>
+          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="4">
         <is>
+          <t xml:space="preserve">Workbook to model bridge</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">After import, use the generated Phase 2 scenario directly or pass the assumptions workbook into the one-command forecast workflow.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions. The workflow also consumes the generated treatment duration artifact when demand_basis = patient_starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="4">
+        <is>
           <t xml:space="preserve">Approved base-case defaults</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">Seeded defaults reflect the current approved Phase 2 base case: fixed dose 0.15 mg, weight-based 0.0023 mg/kg, deterministic average weight 80 kg, AML/MDS 4.33 doses per month, CML modules 1.00 dose per month, fg_mg_per_unit 1.0 mg, DS quantity per DP unit 1.0 mg, ds_to_dp_yield 0.90, dp_to_fg_yield 0.98, ds_overage_factor 0.05, ss_ratio_to_fg 1.0.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="8">
+      <c r="B10" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">Seeded defaults reflect the current approved base case: annual patient_starts for Phase 1, fixed dose 0.15 mg, weight-based 0.0023 mg/kg, deterministic average weight 80 kg, AML/MDS 4.33 doses per month, CML modules 1.00 dose per month, fg_mg_per_unit 1.0 mg, DS quantity per DP unit 1.0 mg, ds_to_dp_yield 0.90, dp_to_fg_yield 0.98, ds_overage_factor 0.05, ss_ratio_to_fg 1.0.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Where the approved contract is still unresolved, rows are labeled PLACEHOLDER rather than silently inventing a final business assumption.</t>
         </is>
@@ -299,6 +317,829 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="72" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">scenario_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">geography_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">addressable_prevalent_pool</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">launch_year_index</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">launch_month_index</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">duration_months</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">curve_profile_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">bolus_start_year</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">bolus_end_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">exhaustion_year</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">exhaustion_rule</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">active_flag</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER_PROFILE</t>
+        </is>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>4</v>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">track_vs_pool</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER populate approved US prevalent pool inputs before activating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER_PROFILE</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>4</v>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">track_vs_pool</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">PLACEHOLDER populate approved EU prevalent pool inputs before activating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="9"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="9"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="9"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="9"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="9"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="9"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="9"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="9"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="9"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="9"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="9"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="9"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="K2:K41" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$N$2:$N$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="M2:M41" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -559,31 +1400,32 @@
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="F2:F21" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,50 +1446,55 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">demand_basis</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">yes_no</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">true_false</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">parameter_scope</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">vialing_rule</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">co_pack_mode</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">active_flag</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">forecast_grain</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">forecast_frequency</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">partial_pack_handling</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">exhaustion_rule</t>
         </is>
@@ -671,50 +1518,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">patient_starts</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">true</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">scenario_default</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_dose_ceiling</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">separate_sku_first</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">module_level</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">monthly</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t xml:space="preserve">annual</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t xml:space="preserve">full_pack_consumed</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">track_vs_pool</t>
         </is>
@@ -738,50 +1590,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">treated_census</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">module_override</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">segment_level</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">annual</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t xml:space="preserve">monthly</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">placeholder_metadata_only</t>
         </is>
@@ -850,6 +1707,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t xml:space="preserve">validate_only</t>
         </is>
       </c>
@@ -920,6 +1782,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -987,6 +1854,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1054,16 +1926,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1072,8 +1949,9 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="56" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1104,15 +1982,20 @@
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">demand_basis</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">dose_basis_default</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">base_currency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -1141,22 +2024,27 @@
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">monthly</t>
+          <t xml:space="preserve">annual</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">patient_starts</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">fixed</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr" s="2">
+      <c r="H2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">Edit this row instead of hand-editing Phase 2 TOML files.</t>
+      <c r="I2" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Edit this row instead of hand-editing config files. Seeded for the annual patient_starts base case.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +2056,8 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="9"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4">
       <c r="A4" s="2"/>
@@ -1178,7 +2067,8 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="9"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5">
       <c r="A5" s="2"/>
@@ -1188,7 +2078,8 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="2"/>
@@ -1198,7 +2089,8 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="9"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
@@ -1208,7 +2100,8 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
@@ -1218,7 +2111,8 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="9"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="2"/>
@@ -1228,7 +2122,8 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="9"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="2"/>
@@ -1238,7 +2133,8 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="9"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="2"/>
@@ -1248,21 +2144,25 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="9"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:I1"/>
+  <dataValidations count="5">
     <dataValidation type="list" sqref="C2:C11" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D2:D11" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
+      <formula1>Lookup_Lists!$K$2:$K$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2:E11" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$K$2:$K$3</formula1>
+      <formula1>Lookup_Lists!$L$2:$L$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F11" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G2:G11" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1776,7 +2676,7 @@
       <formula1>Lookup_Lists!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3632,13 +4532,13 @@
       <formula1>Lookup_Lists!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="J2:J81" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$E$2:$E$3</formula1>
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2:L81" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$E$2:$E$3</formula1>
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="P2:P81" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3646,6 +4546,599 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">scenario_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">module</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">segment_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">geography_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">treatment_duration_months</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">active_flag</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AML</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1L_fit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <v>12</v>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AML</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1L_unfit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AML</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MDS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HR_MDS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MDS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LR_MDS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E6" s="2">
+        <v>12</v>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Incident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Incident</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E7" s="2">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Prevalent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Prevalent</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="E8" s="2">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved base-case duration default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="9"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="B2:B41" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F2:F41" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -4250,20 +5743,20 @@
   <autoFilter ref="A1:J1"/>
   <dataValidations count="3">
     <dataValidation type="list" sqref="B2:B41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
+      <formula1>Lookup_Lists!$G$2:$G$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C2:C41" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$B$2:$B$6</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -4926,20 +6419,20 @@
   <autoFilter ref="A1:K1"/>
   <dataValidations count="3">
     <dataValidation type="list" sqref="B2:B41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
+      <formula1>Lookup_Lists!$G$2:$G$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C2:C41" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$B$2:$B$6</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="J2:J41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5639,23 +7132,23 @@
       <formula1>Lookup_Lists!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D2:D41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$G$2:$G$2</formula1>
+      <formula1>Lookup_Lists!$H$2:$H$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2:F41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$E$2:$E$3</formula1>
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H2:H41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$L$2:$L$2</formula1>
+      <formula1>Lookup_Lists!$M$2:$M$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5917,833 +7410,10 @@
       <formula1>Lookup_Lists!$B$2:$B$6</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2:E21" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$H$2:$H$2</formula1>
+      <formula1>Lookup_Lists!$I$2:$I$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F21" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="72" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">scenario_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">geography_code</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">addressable_prevalent_pool</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">launch_year_index</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">launch_month_index</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">duration_months</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">curve_profile_id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">bolus_start_year</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">bolus_end_year</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">exhaustion_year</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">exhaustion_rule</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">source</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">active_flag</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3">
-        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
-      </c>
-      <c r="B2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">US</t>
-        </is>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>12</v>
-      </c>
-      <c r="G2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER_PROFILE</t>
-        </is>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>4</v>
-      </c>
-      <c r="K2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">track_vs_pool</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER populate approved US prevalent pool inputs before activating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
-      </c>
-      <c r="B3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EU</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>12</v>
-      </c>
-      <c r="G3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER_PROFILE</t>
-        </is>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>4</v>
-      </c>
-      <c r="K3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">track_vs_pool</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER populate approved EU prevalent pool inputs before activating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="9"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="9"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="9"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="9"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="9"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="9"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="9"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="9"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="9"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="9"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="9"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="9"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="9"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="9"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="9"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="9"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="9"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="9"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="9"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="9"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="9"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="9"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="9"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:N1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="K2:K41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$M$2:$M$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="M2:M41" showErrorMessage="1" allowBlank="1">
-      <formula1>Lookup_Lists!$I$2:$I$3</formula1>
+      <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/CBX250_Model_Assumptions_Template.xlsx
+++ b/templates/CBX250_Model_Assumptions_Template.xlsx
@@ -170,7 +170,7 @@
       </c>
       <c r="C2" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Users should edit Excel assumptions here rather than hand-editing TOML files. The importer converts these rows into normalized artifacts plus a generated Phase 2 parameter config.</t>
+          <t xml:space="preserve">Users should edit Excel assumptions here rather than hand-editing TOML files. The importer converts these rows into normalized artifacts plus generated Phase 2 and Phase 3 parameter configs.</t>
         </is>
       </c>
     </row>
@@ -182,12 +182,12 @@
       </c>
       <c r="B3" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current scope covers Phase 1 and Phase 2 relevant assumptions only.</t>
+          <t xml:space="preserve">Current scope covers Phase 1, Phase 2, and the active deterministic Phase 3 trade layer assumptions.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Trade, inventory, production scheduling, financials, Monte Carlo, and UI remain later-phase work. FutureHooks rows are preserved but not wired into active logic.</t>
+          <t xml:space="preserve">Production scheduling, inventory, financials, Monte Carlo, and UI remain later-phase work. Trade_Inventory_FutureHooks now wires the active deterministic Phase 3 trade config, but broader future-phase inventory behavior remains deferred.</t>
         </is>
       </c>
     </row>
@@ -250,12 +250,12 @@
       </c>
       <c r="B7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml and generated_phase2_scenario.toml.</t>
+          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml / generated_phase2_scenario.toml and generated_phase3_parameters.toml / generated_phase3_scenario.toml.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode, and dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2.</t>
+          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode; dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2; and active deterministic trade parameters from Trade_Inventory_FutureHooks for Phase 3.</t>
         </is>
       </c>
     </row>
@@ -267,12 +267,12 @@
       </c>
       <c r="B8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Launch_Timing, geography-specific overrides, segment-specific overrides, dp_concentration_mg_per_ml, dp_fill_volume_ml, and Trade_Inventory_FutureHooks are preserved in normalized outputs even if not yet wired into active model logic.</t>
+          <t xml:space="preserve">Launch_Timing, geography-specific overrides, segment-specific overrides, dp_concentration_mg_per_ml, and dp_fill_volume_ml are preserved in normalized outputs even if not yet wired into active model logic.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic.</t>
+          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic. Trade_Inventory_FutureHooks still carries a historical name, but it now also feeds the active deterministic Phase 3 trade config.</t>
         </is>
       </c>
     </row>
@@ -284,12 +284,12 @@
       </c>
       <c r="B9" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">After import, use the generated Phase 2 scenario directly or pass the assumptions workbook into the one-command forecast workflow.</t>
+          <t xml:space="preserve">After import, use the generated Phase 2 or Phase 3 scenario directly, or pass the assumptions workbook into the one-command forecast workflow.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions. The workflow also consumes the generated treatment duration artifact when demand_basis = patient_starts.</t>
+          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions. The workflow also consumes the generated treatment duration artifact when demand_basis = patient_starts and can optionally run through Phase 3.</t>
         </is>
       </c>
     </row>
@@ -1141,16 +1141,32 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="68" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1161,30 +1177,110 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">trade_row_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">module</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">geography_code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">trade_rule_placeholder</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">inventory_rule_placeholder</t>
+          <t xml:space="preserve">sublayer1_target_weeks_on_hand</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">sublayer2_target_weeks_on_hand</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">sublayer2_wastage_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">initial_stocking_units_per_new_site</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_units_per_new_site</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">sublayer1_launch_fill_months_of_demand</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">rems_certification_lag_weeks</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">january_softening_enabled</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">january_softening_factor</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">bullwhip_flag_threshold</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">channel_fill_start_prelaunch_weeks</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">sublayer2_fill_distribution_weeks</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">weeks_per_month</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">site_activation_rate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">certified_sites_at_launch</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">certified_sites_at_peak</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">launch_month_index</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">active_flag</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="W1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -1196,124 +1292,572 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">scenario_default</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ALL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ALL</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER_FUTURE_PHASE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PLACEHOLDER_FUTURE_PHASE</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">Future-phase placeholders only. Not wired into active model logic.</t>
+      <c r="E2" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O2" s="2">
+        <v>4</v>
+      </c>
+      <c r="P2" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>4.33</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved deterministic Phase 3 scenario defaults. Edit here instead of phase3_trade_layer.toml.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">geography_default</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2">
+        <v>5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5</v>
+      </c>
+      <c r="T3" s="2">
+        <v>25</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample US site activation defaults for the deterministic Phase 3 trade layer.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">geography_default</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2">
+        <v>3</v>
+      </c>
+      <c r="S4" s="2">
+        <v>3</v>
+      </c>
+      <c r="T4" s="2">
+        <v>18</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample EU site activation defaults for the deterministic Phase 3 trade layer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AML</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="9"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MDS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="9"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Incident</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="9"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Prevalent</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">US</t>
+        </is>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="9"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AML</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="9"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MDS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="9"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Incident</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="9"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="3">
+        <f>IF(Scenario_Controls!$A$2="","",Scenario_Controls!$A$2)</f>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CML_Prevalent</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EU</t>
+        </is>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="9"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Approved/sample launch event.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -1322,7 +1866,23 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="9"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -1331,7 +1891,23 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="9"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="9"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -1340,7 +1916,23 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="9"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -1349,7 +1941,23 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="9"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="9"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -1358,7 +1966,23 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="9"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -1367,7 +1991,23 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="9"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="9"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -1376,7 +2016,23 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="9"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -1385,7 +2041,23 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="9"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -1394,12 +2066,37 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="9"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F21" showErrorMessage="1" allowBlank="1">
+  <autoFilter ref="A1:W1"/>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="B2:B21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$O$2:$O$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C2:C21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$B$2:$B$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2:L21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="V2:V21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1409,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1426,6 +2123,7 @@
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
     <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1499,6 +2197,11 @@
           <t xml:space="preserve">exhaustion_rule</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">trade_row_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1571,6 +2274,11 @@
           <t xml:space="preserve">track_vs_pool</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scenario_default</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1643,6 +2351,11 @@
           <t xml:space="preserve">placeholder_metadata_only</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geography_default</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1715,6 +2428,11 @@
           <t xml:space="preserve">validate_only</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">launch_event</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1787,6 +2505,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1859,6 +2582,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1931,9 +2659,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/templates/CBX250_Model_Assumptions_Template.xlsx
+++ b/templates/CBX250_Model_Assumptions_Template.xlsx
@@ -182,12 +182,12 @@
       </c>
       <c r="B3" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current scope covers Phase 1, Phase 2, and the active deterministic Phase 3 trade layer assumptions.</t>
+          <t xml:space="preserve">Current scope covers Phase 1, Phase 2, and the active deterministic Phase 3, Phase 4, and Phase 5 assumptions.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Production scheduling, inventory, financials, Monte Carlo, and UI remain later-phase work. Trade_Inventory_FutureHooks now wires the active deterministic Phase 3 trade config, but broader future-phase inventory behavior remains deferred.</t>
+          <t xml:space="preserve">Financials, Monte Carlo, and UI remain later-phase work. Trade_Inventory_FutureHooks now wires the active deterministic Phase 3 trade config plus the active deterministic Phase 4 scheduling and Phase 5 inventory configs.</t>
         </is>
       </c>
     </row>
@@ -250,12 +250,12 @@
       </c>
       <c r="B7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml / generated_phase2_scenario.toml and generated_phase3_parameters.toml / generated_phase3_scenario.toml.</t>
+          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml / generated_phase2_scenario.toml, generated_phase3_parameters.toml / generated_phase3_scenario.toml, generated_phase4_parameters.toml / generated_phase4_scenario.toml, and generated_phase5_parameters.toml / generated_phase5_scenario.toml.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode; dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2; and active deterministic trade parameters from Trade_Inventory_FutureHooks for Phase 3.</t>
+          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode; dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2; active deterministic trade parameters from Trade_Inventory_FutureHooks for Phase 3; and active deterministic Phase 4 scheduling plus Phase 5 inventory controls from Trade_Inventory_FutureHooks together with the scenario-default Product_Parameters, Yield_Assumptions, and SS_Assumptions rows.</t>
         </is>
       </c>
     </row>
@@ -272,7 +272,7 @@
       </c>
       <c r="C8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic. Trade_Inventory_FutureHooks still carries a historical name, but it now also feeds the active deterministic Phase 3 trade config.</t>
+          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic. Trade_Inventory_FutureHooks still carries a historical name, but it now also feeds the active deterministic Phase 3 trade config plus the active Phase 4 scheduling and Phase 5 inventory config bridges.</t>
         </is>
       </c>
     </row>
@@ -289,7 +289,7 @@
       </c>
       <c r="C9" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions. The workflow also consumes the generated treatment duration artifact when demand_basis = patient_starts and can optionally run through Phase 3.</t>
+          <t xml:space="preserve">This keeps the current architecture intact while removing the need to edit TOML by hand for the active deterministic assumptions. The workflow also consumes the generated treatment duration artifact when demand_basis = patient_starts and can optionally run through Phase 5.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:BV21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1165,8 +1165,58 @@
     <col min="19" max="19" width="20" customWidth="1"/>
     <col min="20" max="20" width="20" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="72" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="38" width="20" customWidth="1"/>
+    <col min="39" max="39" width="20" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="18" customWidth="1"/>
+    <col min="43" max="43" width="22" customWidth="1"/>
+    <col min="44" max="44" width="18" customWidth="1"/>
+    <col min="45" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="18" customWidth="1"/>
+    <col min="47" max="47" width="18" customWidth="1"/>
+    <col min="48" max="48" width="18" customWidth="1"/>
+    <col min="49" max="49" width="18" customWidth="1"/>
+    <col min="50" max="50" width="18" customWidth="1"/>
+    <col min="51" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="18" customWidth="1"/>
+    <col min="53" max="53" width="18" customWidth="1"/>
+    <col min="54" max="54" width="18" customWidth="1"/>
+    <col min="55" max="55" width="18" customWidth="1"/>
+    <col min="56" max="56" width="18" customWidth="1"/>
+    <col min="57" max="57" width="18" customWidth="1"/>
+    <col min="58" max="58" width="18" customWidth="1"/>
+    <col min="59" max="59" width="18" customWidth="1"/>
+    <col min="60" max="60" width="18" customWidth="1"/>
+    <col min="61" max="61" width="18" customWidth="1"/>
+    <col min="62" max="62" width="18" customWidth="1"/>
+    <col min="63" max="63" width="18" customWidth="1"/>
+    <col min="64" max="64" width="18" customWidth="1"/>
+    <col min="65" max="65" width="18" customWidth="1"/>
+    <col min="66" max="66" width="18" customWidth="1"/>
+    <col min="67" max="67" width="18" customWidth="1"/>
+    <col min="68" max="68" width="18" customWidth="1"/>
+    <col min="69" max="69" width="18" customWidth="1"/>
+    <col min="70" max="70" width="18" customWidth="1"/>
+    <col min="71" max="71" width="18" customWidth="1"/>
+    <col min="72" max="72" width="12" customWidth="1"/>
+    <col min="73" max="73" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1277,10 +1327,265 @@
       </c>
       <c r="V1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">bullwhip_amplification_threshold</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">bullwhip_review_window_months</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">excess_build_threshold_ratio</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">supply_gap_tolerance_units</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">capacity_clip_tolerance_units</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">cml_prevalent_forward_window_months</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">projected_cml_prevalent_bolus_exhaustion_month_index</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_lead_time_from_dp_release_weeks</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_packaging_cycle_weeks</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_release_qa_weeks</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_total_order_to_release_weeks</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_packaging_campaign_size_units</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_lead_time_from_ds_release_weeks</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_manufacturing_cycle_weeks</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_release_testing_weeks</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_total_order_to_release_weeks</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_min_batch_size_units</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_max_batch_size_units</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_min_campaign_batches</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_annual_capacity_batches</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_lead_time_to_batch_start_planning_horizon_weeks</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_manufacturing_cycle_weeks</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_release_testing_weeks</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_total_order_to_release_weeks</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_min_batch_size_kg</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_max_batch_size_kg</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_min_campaign_batches</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_annual_capacity_batches</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_order_to_release_lead_time_weeks</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_batch_size_units</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_min_campaign_batches</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_annual_capacity_batches</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_release_must_coincide_with_or_precede_fg</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_ds_mg</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_dp_units</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_fg_units</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_ss_units</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_sublayer1_fg_units</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">starting_inventory_sublayer2_fg_units</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">shelf_life_ds_months</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">shelf_life_dp_months</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">shelf_life_fg_months</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">shelf_life_ss_months</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">excess_inventory_threshold_months_of_cover</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">stockout_tolerance_units</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fefo_enabled</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_fg_match_required</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">allow_prelaunch_inventory_build</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">phase5_enforce_unique_output_keys</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">phase5_reconcile_phase4_receipts</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">phase5_reconciliation_tolerance_units</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">active_flag</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr" s="1">
+      <c r="BV1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -1350,14 +1655,179 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" t="inlineStr" s="2">
+      <c r="V2" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W2" s="2">
+        <v>2</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1e-06</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>1e-06</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>8</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AJ2" s="2">
+        <v>12</v>
+      </c>
+      <c r="AK2" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="AM2" s="2">
+        <v>500000</v>
+      </c>
+      <c r="AN2" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO2" s="2">
+        <v>10</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>24</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>8</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>12</v>
+      </c>
+      <c r="AS2" s="2">
+        <v>44</v>
+      </c>
+      <c r="AT2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AU2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AV2" s="2">
+        <v>3</v>
+      </c>
+      <c r="AW2" s="2">
+        <v>5</v>
+      </c>
+      <c r="AX2" s="2">
+        <v>24</v>
+      </c>
+      <c r="AY2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="AZ2" s="2">
+        <v>3</v>
+      </c>
+      <c r="BA2" s="2">
+        <v>10</v>
+      </c>
+      <c r="BB2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>24</v>
+      </c>
+      <c r="BJ2" s="2">
+        <v>24</v>
+      </c>
+      <c r="BK2" s="2">
+        <v>24</v>
+      </c>
+      <c r="BL2" s="2">
+        <v>24</v>
+      </c>
+      <c r="BM2" s="2">
+        <v>6</v>
+      </c>
+      <c r="BN2" s="2">
+        <v>1e-06</v>
+      </c>
+      <c r="BO2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="BT2" s="2">
+        <v>1e-06</v>
+      </c>
+      <c r="BU2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">Approved deterministic Phase 3 scenario defaults. Edit here instead of phase3_trade_layer.toml.</t>
+      <c r="BV2" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">Active deterministic defaults for Phase 3, Phase 4, and Phase 5. Edit here instead of hand-editing phase3_trade_layer.toml, phase4_production_schedule.toml, or phase5_inventory_layer.toml.</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1873,63 @@
         <v>25</v>
       </c>
       <c r="U3" s="2"/>
-      <c r="V3" t="inlineStr" s="2">
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2"/>
+      <c r="AW3" s="2"/>
+      <c r="AX3" s="2"/>
+      <c r="AY3" s="2"/>
+      <c r="AZ3" s="2"/>
+      <c r="BA3" s="2"/>
+      <c r="BB3" s="2"/>
+      <c r="BC3" s="2"/>
+      <c r="BD3" s="2"/>
+      <c r="BE3" s="2"/>
+      <c r="BF3" s="2"/>
+      <c r="BG3" s="2"/>
+      <c r="BH3" s="2"/>
+      <c r="BI3" s="2"/>
+      <c r="BJ3" s="2"/>
+      <c r="BK3" s="2"/>
+      <c r="BL3" s="2"/>
+      <c r="BM3" s="2"/>
+      <c r="BN3" s="2"/>
+      <c r="BO3" s="2"/>
+      <c r="BP3" s="2"/>
+      <c r="BQ3" s="2"/>
+      <c r="BR3" s="2"/>
+      <c r="BS3" s="2"/>
+      <c r="BT3" s="2"/>
+      <c r="BU3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr" s="9">
+      <c r="BV3" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample US site activation defaults for the deterministic Phase 3 trade layer.</t>
         </is>
@@ -1456,12 +1977,63 @@
         <v>18</v>
       </c>
       <c r="U4" s="2"/>
-      <c r="V4" t="inlineStr" s="2">
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+      <c r="BU4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr" s="9">
+      <c r="BV4" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample EU site activation defaults for the deterministic Phase 3 trade layer.</t>
         </is>
@@ -1505,12 +2077,63 @@
       <c r="U5" s="2">
         <v>1</v>
       </c>
-      <c r="V5" t="inlineStr" s="2">
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2"/>
+      <c r="BF5" s="2"/>
+      <c r="BG5" s="2"/>
+      <c r="BH5" s="2"/>
+      <c r="BI5" s="2"/>
+      <c r="BJ5" s="2"/>
+      <c r="BK5" s="2"/>
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2"/>
+      <c r="BO5" s="2"/>
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2"/>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2"/>
+      <c r="BT5" s="2"/>
+      <c r="BU5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr" s="9">
+      <c r="BV5" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1554,12 +2177,63 @@
       <c r="U6" s="2">
         <v>1</v>
       </c>
-      <c r="V6" t="inlineStr" s="2">
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="2"/>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2"/>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2"/>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2"/>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2"/>
+      <c r="BF6" s="2"/>
+      <c r="BG6" s="2"/>
+      <c r="BH6" s="2"/>
+      <c r="BI6" s="2"/>
+      <c r="BJ6" s="2"/>
+      <c r="BK6" s="2"/>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2"/>
+      <c r="BO6" s="2"/>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2"/>
+      <c r="BR6" s="2"/>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2"/>
+      <c r="BU6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr" s="9">
+      <c r="BV6" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1603,12 +2277,63 @@
       <c r="U7" s="2">
         <v>1</v>
       </c>
-      <c r="V7" t="inlineStr" s="2">
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="2"/>
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2"/>
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2"/>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2"/>
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2"/>
+      <c r="BF7" s="2"/>
+      <c r="BG7" s="2"/>
+      <c r="BH7" s="2"/>
+      <c r="BI7" s="2"/>
+      <c r="BJ7" s="2"/>
+      <c r="BK7" s="2"/>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2"/>
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2"/>
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2"/>
+      <c r="BU7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr" s="9">
+      <c r="BV7" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1652,12 +2377,63 @@
       <c r="U8" s="2">
         <v>1</v>
       </c>
-      <c r="V8" t="inlineStr" s="2">
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="2"/>
+      <c r="AM8" s="2"/>
+      <c r="AN8" s="2"/>
+      <c r="AO8" s="2"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="2"/>
+      <c r="AT8" s="2"/>
+      <c r="AU8" s="2"/>
+      <c r="AV8" s="2"/>
+      <c r="AW8" s="2"/>
+      <c r="AX8" s="2"/>
+      <c r="AY8" s="2"/>
+      <c r="AZ8" s="2"/>
+      <c r="BA8" s="2"/>
+      <c r="BB8" s="2"/>
+      <c r="BC8" s="2"/>
+      <c r="BD8" s="2"/>
+      <c r="BE8" s="2"/>
+      <c r="BF8" s="2"/>
+      <c r="BG8" s="2"/>
+      <c r="BH8" s="2"/>
+      <c r="BI8" s="2"/>
+      <c r="BJ8" s="2"/>
+      <c r="BK8" s="2"/>
+      <c r="BL8" s="2"/>
+      <c r="BM8" s="2"/>
+      <c r="BN8" s="2"/>
+      <c r="BO8" s="2"/>
+      <c r="BP8" s="2"/>
+      <c r="BQ8" s="2"/>
+      <c r="BR8" s="2"/>
+      <c r="BS8" s="2"/>
+      <c r="BT8" s="2"/>
+      <c r="BU8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr" s="9">
+      <c r="BV8" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1701,12 +2477,63 @@
       <c r="U9" s="2">
         <v>1</v>
       </c>
-      <c r="V9" t="inlineStr" s="2">
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
+      <c r="AU9" s="2"/>
+      <c r="AV9" s="2"/>
+      <c r="AW9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="AY9" s="2"/>
+      <c r="AZ9" s="2"/>
+      <c r="BA9" s="2"/>
+      <c r="BB9" s="2"/>
+      <c r="BC9" s="2"/>
+      <c r="BD9" s="2"/>
+      <c r="BE9" s="2"/>
+      <c r="BF9" s="2"/>
+      <c r="BG9" s="2"/>
+      <c r="BH9" s="2"/>
+      <c r="BI9" s="2"/>
+      <c r="BJ9" s="2"/>
+      <c r="BK9" s="2"/>
+      <c r="BL9" s="2"/>
+      <c r="BM9" s="2"/>
+      <c r="BN9" s="2"/>
+      <c r="BO9" s="2"/>
+      <c r="BP9" s="2"/>
+      <c r="BQ9" s="2"/>
+      <c r="BR9" s="2"/>
+      <c r="BS9" s="2"/>
+      <c r="BT9" s="2"/>
+      <c r="BU9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr" s="9">
+      <c r="BV9" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1750,12 +2577,63 @@
       <c r="U10" s="2">
         <v>1</v>
       </c>
-      <c r="V10" t="inlineStr" s="2">
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
+      <c r="AL10" s="2"/>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2"/>
+      <c r="AS10" s="2"/>
+      <c r="AT10" s="2"/>
+      <c r="AU10" s="2"/>
+      <c r="AV10" s="2"/>
+      <c r="AW10" s="2"/>
+      <c r="AX10" s="2"/>
+      <c r="AY10" s="2"/>
+      <c r="AZ10" s="2"/>
+      <c r="BA10" s="2"/>
+      <c r="BB10" s="2"/>
+      <c r="BC10" s="2"/>
+      <c r="BD10" s="2"/>
+      <c r="BE10" s="2"/>
+      <c r="BF10" s="2"/>
+      <c r="BG10" s="2"/>
+      <c r="BH10" s="2"/>
+      <c r="BI10" s="2"/>
+      <c r="BJ10" s="2"/>
+      <c r="BK10" s="2"/>
+      <c r="BL10" s="2"/>
+      <c r="BM10" s="2"/>
+      <c r="BN10" s="2"/>
+      <c r="BO10" s="2"/>
+      <c r="BP10" s="2"/>
+      <c r="BQ10" s="2"/>
+      <c r="BR10" s="2"/>
+      <c r="BS10" s="2"/>
+      <c r="BT10" s="2"/>
+      <c r="BU10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr" s="9">
+      <c r="BV10" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1799,12 +2677,63 @@
       <c r="U11" s="2">
         <v>1</v>
       </c>
-      <c r="V11" t="inlineStr" s="2">
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="2"/>
+      <c r="AG11" s="2"/>
+      <c r="AH11" s="2"/>
+      <c r="AI11" s="2"/>
+      <c r="AJ11" s="2"/>
+      <c r="AK11" s="2"/>
+      <c r="AL11" s="2"/>
+      <c r="AM11" s="2"/>
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="2"/>
+      <c r="AS11" s="2"/>
+      <c r="AT11" s="2"/>
+      <c r="AU11" s="2"/>
+      <c r="AV11" s="2"/>
+      <c r="AW11" s="2"/>
+      <c r="AX11" s="2"/>
+      <c r="AY11" s="2"/>
+      <c r="AZ11" s="2"/>
+      <c r="BA11" s="2"/>
+      <c r="BB11" s="2"/>
+      <c r="BC11" s="2"/>
+      <c r="BD11" s="2"/>
+      <c r="BE11" s="2"/>
+      <c r="BF11" s="2"/>
+      <c r="BG11" s="2"/>
+      <c r="BH11" s="2"/>
+      <c r="BI11" s="2"/>
+      <c r="BJ11" s="2"/>
+      <c r="BK11" s="2"/>
+      <c r="BL11" s="2"/>
+      <c r="BM11" s="2"/>
+      <c r="BN11" s="2"/>
+      <c r="BO11" s="2"/>
+      <c r="BP11" s="2"/>
+      <c r="BQ11" s="2"/>
+      <c r="BR11" s="2"/>
+      <c r="BS11" s="2"/>
+      <c r="BT11" s="2"/>
+      <c r="BU11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr" s="9">
+      <c r="BV11" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1848,12 +2777,63 @@
       <c r="U12" s="2">
         <v>1</v>
       </c>
-      <c r="V12" t="inlineStr" s="2">
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="2"/>
+      <c r="AG12" s="2"/>
+      <c r="AH12" s="2"/>
+      <c r="AI12" s="2"/>
+      <c r="AJ12" s="2"/>
+      <c r="AK12" s="2"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+      <c r="AP12" s="2"/>
+      <c r="AQ12" s="2"/>
+      <c r="AR12" s="2"/>
+      <c r="AS12" s="2"/>
+      <c r="AT12" s="2"/>
+      <c r="AU12" s="2"/>
+      <c r="AV12" s="2"/>
+      <c r="AW12" s="2"/>
+      <c r="AX12" s="2"/>
+      <c r="AY12" s="2"/>
+      <c r="AZ12" s="2"/>
+      <c r="BA12" s="2"/>
+      <c r="BB12" s="2"/>
+      <c r="BC12" s="2"/>
+      <c r="BD12" s="2"/>
+      <c r="BE12" s="2"/>
+      <c r="BF12" s="2"/>
+      <c r="BG12" s="2"/>
+      <c r="BH12" s="2"/>
+      <c r="BI12" s="2"/>
+      <c r="BJ12" s="2"/>
+      <c r="BK12" s="2"/>
+      <c r="BL12" s="2"/>
+      <c r="BM12" s="2"/>
+      <c r="BN12" s="2"/>
+      <c r="BO12" s="2"/>
+      <c r="BP12" s="2"/>
+      <c r="BQ12" s="2"/>
+      <c r="BR12" s="2"/>
+      <c r="BS12" s="2"/>
+      <c r="BT12" s="2"/>
+      <c r="BU12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr" s="9">
+      <c r="BV12" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
@@ -1882,7 +2862,58 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
-      <c r="W13" s="9"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+      <c r="AP13" s="2"/>
+      <c r="AQ13" s="2"/>
+      <c r="AR13" s="2"/>
+      <c r="AS13" s="2"/>
+      <c r="AT13" s="2"/>
+      <c r="AU13" s="2"/>
+      <c r="AV13" s="2"/>
+      <c r="AW13" s="2"/>
+      <c r="AX13" s="2"/>
+      <c r="AY13" s="2"/>
+      <c r="AZ13" s="2"/>
+      <c r="BA13" s="2"/>
+      <c r="BB13" s="2"/>
+      <c r="BC13" s="2"/>
+      <c r="BD13" s="2"/>
+      <c r="BE13" s="2"/>
+      <c r="BF13" s="2"/>
+      <c r="BG13" s="2"/>
+      <c r="BH13" s="2"/>
+      <c r="BI13" s="2"/>
+      <c r="BJ13" s="2"/>
+      <c r="BK13" s="2"/>
+      <c r="BL13" s="2"/>
+      <c r="BM13" s="2"/>
+      <c r="BN13" s="2"/>
+      <c r="BO13" s="2"/>
+      <c r="BP13" s="2"/>
+      <c r="BQ13" s="2"/>
+      <c r="BR13" s="2"/>
+      <c r="BS13" s="2"/>
+      <c r="BT13" s="2"/>
+      <c r="BU13" s="2"/>
+      <c r="BV13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -1907,7 +2938,58 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
-      <c r="W14" s="9"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
+      <c r="AI14" s="2"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="2"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+      <c r="AP14" s="2"/>
+      <c r="AQ14" s="2"/>
+      <c r="AR14" s="2"/>
+      <c r="AS14" s="2"/>
+      <c r="AT14" s="2"/>
+      <c r="AU14" s="2"/>
+      <c r="AV14" s="2"/>
+      <c r="AW14" s="2"/>
+      <c r="AX14" s="2"/>
+      <c r="AY14" s="2"/>
+      <c r="AZ14" s="2"/>
+      <c r="BA14" s="2"/>
+      <c r="BB14" s="2"/>
+      <c r="BC14" s="2"/>
+      <c r="BD14" s="2"/>
+      <c r="BE14" s="2"/>
+      <c r="BF14" s="2"/>
+      <c r="BG14" s="2"/>
+      <c r="BH14" s="2"/>
+      <c r="BI14" s="2"/>
+      <c r="BJ14" s="2"/>
+      <c r="BK14" s="2"/>
+      <c r="BL14" s="2"/>
+      <c r="BM14" s="2"/>
+      <c r="BN14" s="2"/>
+      <c r="BO14" s="2"/>
+      <c r="BP14" s="2"/>
+      <c r="BQ14" s="2"/>
+      <c r="BR14" s="2"/>
+      <c r="BS14" s="2"/>
+      <c r="BT14" s="2"/>
+      <c r="BU14" s="2"/>
+      <c r="BV14" s="9"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -1932,7 +3014,58 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
-      <c r="W15" s="9"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+      <c r="AP15" s="2"/>
+      <c r="AQ15" s="2"/>
+      <c r="AR15" s="2"/>
+      <c r="AS15" s="2"/>
+      <c r="AT15" s="2"/>
+      <c r="AU15" s="2"/>
+      <c r="AV15" s="2"/>
+      <c r="AW15" s="2"/>
+      <c r="AX15" s="2"/>
+      <c r="AY15" s="2"/>
+      <c r="AZ15" s="2"/>
+      <c r="BA15" s="2"/>
+      <c r="BB15" s="2"/>
+      <c r="BC15" s="2"/>
+      <c r="BD15" s="2"/>
+      <c r="BE15" s="2"/>
+      <c r="BF15" s="2"/>
+      <c r="BG15" s="2"/>
+      <c r="BH15" s="2"/>
+      <c r="BI15" s="2"/>
+      <c r="BJ15" s="2"/>
+      <c r="BK15" s="2"/>
+      <c r="BL15" s="2"/>
+      <c r="BM15" s="2"/>
+      <c r="BN15" s="2"/>
+      <c r="BO15" s="2"/>
+      <c r="BP15" s="2"/>
+      <c r="BQ15" s="2"/>
+      <c r="BR15" s="2"/>
+      <c r="BS15" s="2"/>
+      <c r="BT15" s="2"/>
+      <c r="BU15" s="2"/>
+      <c r="BV15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -1957,7 +3090,58 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
-      <c r="W16" s="9"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+      <c r="AP16" s="2"/>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2"/>
+      <c r="AT16" s="2"/>
+      <c r="AU16" s="2"/>
+      <c r="AV16" s="2"/>
+      <c r="AW16" s="2"/>
+      <c r="AX16" s="2"/>
+      <c r="AY16" s="2"/>
+      <c r="AZ16" s="2"/>
+      <c r="BA16" s="2"/>
+      <c r="BB16" s="2"/>
+      <c r="BC16" s="2"/>
+      <c r="BD16" s="2"/>
+      <c r="BE16" s="2"/>
+      <c r="BF16" s="2"/>
+      <c r="BG16" s="2"/>
+      <c r="BH16" s="2"/>
+      <c r="BI16" s="2"/>
+      <c r="BJ16" s="2"/>
+      <c r="BK16" s="2"/>
+      <c r="BL16" s="2"/>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="2"/>
+      <c r="BO16" s="2"/>
+      <c r="BP16" s="2"/>
+      <c r="BQ16" s="2"/>
+      <c r="BR16" s="2"/>
+      <c r="BS16" s="2"/>
+      <c r="BT16" s="2"/>
+      <c r="BU16" s="2"/>
+      <c r="BV16" s="9"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -1982,7 +3166,58 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="9"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="2"/>
+      <c r="AU17" s="2"/>
+      <c r="AV17" s="2"/>
+      <c r="AW17" s="2"/>
+      <c r="AX17" s="2"/>
+      <c r="AY17" s="2"/>
+      <c r="AZ17" s="2"/>
+      <c r="BA17" s="2"/>
+      <c r="BB17" s="2"/>
+      <c r="BC17" s="2"/>
+      <c r="BD17" s="2"/>
+      <c r="BE17" s="2"/>
+      <c r="BF17" s="2"/>
+      <c r="BG17" s="2"/>
+      <c r="BH17" s="2"/>
+      <c r="BI17" s="2"/>
+      <c r="BJ17" s="2"/>
+      <c r="BK17" s="2"/>
+      <c r="BL17" s="2"/>
+      <c r="BM17" s="2"/>
+      <c r="BN17" s="2"/>
+      <c r="BO17" s="2"/>
+      <c r="BP17" s="2"/>
+      <c r="BQ17" s="2"/>
+      <c r="BR17" s="2"/>
+      <c r="BS17" s="2"/>
+      <c r="BT17" s="2"/>
+      <c r="BU17" s="2"/>
+      <c r="BV17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -2007,7 +3242,58 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="9"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="2"/>
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2"/>
+      <c r="AV18" s="2"/>
+      <c r="AW18" s="2"/>
+      <c r="AX18" s="2"/>
+      <c r="AY18" s="2"/>
+      <c r="AZ18" s="2"/>
+      <c r="BA18" s="2"/>
+      <c r="BB18" s="2"/>
+      <c r="BC18" s="2"/>
+      <c r="BD18" s="2"/>
+      <c r="BE18" s="2"/>
+      <c r="BF18" s="2"/>
+      <c r="BG18" s="2"/>
+      <c r="BH18" s="2"/>
+      <c r="BI18" s="2"/>
+      <c r="BJ18" s="2"/>
+      <c r="BK18" s="2"/>
+      <c r="BL18" s="2"/>
+      <c r="BM18" s="2"/>
+      <c r="BN18" s="2"/>
+      <c r="BO18" s="2"/>
+      <c r="BP18" s="2"/>
+      <c r="BQ18" s="2"/>
+      <c r="BR18" s="2"/>
+      <c r="BS18" s="2"/>
+      <c r="BT18" s="2"/>
+      <c r="BU18" s="2"/>
+      <c r="BV18" s="9"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -2032,7 +3318,58 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="9"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="2"/>
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="2"/>
+      <c r="AU19" s="2"/>
+      <c r="AV19" s="2"/>
+      <c r="AW19" s="2"/>
+      <c r="AX19" s="2"/>
+      <c r="AY19" s="2"/>
+      <c r="AZ19" s="2"/>
+      <c r="BA19" s="2"/>
+      <c r="BB19" s="2"/>
+      <c r="BC19" s="2"/>
+      <c r="BD19" s="2"/>
+      <c r="BE19" s="2"/>
+      <c r="BF19" s="2"/>
+      <c r="BG19" s="2"/>
+      <c r="BH19" s="2"/>
+      <c r="BI19" s="2"/>
+      <c r="BJ19" s="2"/>
+      <c r="BK19" s="2"/>
+      <c r="BL19" s="2"/>
+      <c r="BM19" s="2"/>
+      <c r="BN19" s="2"/>
+      <c r="BO19" s="2"/>
+      <c r="BP19" s="2"/>
+      <c r="BQ19" s="2"/>
+      <c r="BR19" s="2"/>
+      <c r="BS19" s="2"/>
+      <c r="BT19" s="2"/>
+      <c r="BU19" s="2"/>
+      <c r="BV19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -2057,7 +3394,58 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="9"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="2"/>
+      <c r="AL20" s="2"/>
+      <c r="AM20" s="2"/>
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+      <c r="AT20" s="2"/>
+      <c r="AU20" s="2"/>
+      <c r="AV20" s="2"/>
+      <c r="AW20" s="2"/>
+      <c r="AX20" s="2"/>
+      <c r="AY20" s="2"/>
+      <c r="AZ20" s="2"/>
+      <c r="BA20" s="2"/>
+      <c r="BB20" s="2"/>
+      <c r="BC20" s="2"/>
+      <c r="BD20" s="2"/>
+      <c r="BE20" s="2"/>
+      <c r="BF20" s="2"/>
+      <c r="BG20" s="2"/>
+      <c r="BH20" s="2"/>
+      <c r="BI20" s="2"/>
+      <c r="BJ20" s="2"/>
+      <c r="BK20" s="2"/>
+      <c r="BL20" s="2"/>
+      <c r="BM20" s="2"/>
+      <c r="BN20" s="2"/>
+      <c r="BO20" s="2"/>
+      <c r="BP20" s="2"/>
+      <c r="BQ20" s="2"/>
+      <c r="BR20" s="2"/>
+      <c r="BS20" s="2"/>
+      <c r="BT20" s="2"/>
+      <c r="BU20" s="2"/>
+      <c r="BV20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -2082,11 +3470,62 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="9"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="2"/>
+      <c r="AL21" s="2"/>
+      <c r="AM21" s="2"/>
+      <c r="AN21" s="2"/>
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="2"/>
+      <c r="AU21" s="2"/>
+      <c r="AV21" s="2"/>
+      <c r="AW21" s="2"/>
+      <c r="AX21" s="2"/>
+      <c r="AY21" s="2"/>
+      <c r="AZ21" s="2"/>
+      <c r="BA21" s="2"/>
+      <c r="BB21" s="2"/>
+      <c r="BC21" s="2"/>
+      <c r="BD21" s="2"/>
+      <c r="BE21" s="2"/>
+      <c r="BF21" s="2"/>
+      <c r="BG21" s="2"/>
+      <c r="BH21" s="2"/>
+      <c r="BI21" s="2"/>
+      <c r="BJ21" s="2"/>
+      <c r="BK21" s="2"/>
+      <c r="BL21" s="2"/>
+      <c r="BM21" s="2"/>
+      <c r="BN21" s="2"/>
+      <c r="BO21" s="2"/>
+      <c r="BP21" s="2"/>
+      <c r="BQ21" s="2"/>
+      <c r="BR21" s="2"/>
+      <c r="BS21" s="2"/>
+      <c r="BT21" s="2"/>
+      <c r="BU21" s="2"/>
+      <c r="BV21" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:BV1"/>
+  <dataValidations count="6">
     <dataValidation type="list" sqref="B2:B21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$O$2:$O$4</formula1>
     </dataValidation>
@@ -2096,7 +3535,13 @@
     <dataValidation type="list" sqref="L2:L21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="V2:V21" showErrorMessage="1" allowBlank="1">
+    <dataValidation type="list" sqref="BB2:BB21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="BO2:BS21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="BU2:BU21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/CBX250_Model_Assumptions_Template.xlsx
+++ b/templates/CBX250_Model_Assumptions_Template.xlsx
@@ -1775,19 +1775,19 @@
         <v>0</v>
       </c>
       <c r="BI2" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="BJ2" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BK2" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BL2" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="BM2" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BN2" s="2">
         <v>1e-06</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="BV2" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Active deterministic defaults for Phase 3, Phase 4, and Phase 5. Edit here instead of hand-editing phase3_trade_layer.toml, phase4_production_schedule.toml, or phase5_inventory_layer.toml.</t>
+          <t xml:space="preserve">Active deterministic defaults for Phase 3, Phase 4, and Phase 5. Phase 5 shelf life and excess-cover values are revised placeholder baseline assumptions; edit here instead of hand-editing phase3_trade_layer.toml, phase4_production_schedule.toml, or phase5_inventory_layer.toml.</t>
         </is>
       </c>
     </row>

--- a/templates/CBX250_Model_Assumptions_Template.xlsx
+++ b/templates/CBX250_Model_Assumptions_Template.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="C3" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Financials, Monte Carlo, and UI remain later-phase work. Trade_Inventory_FutureHooks now wires the active deterministic Phase 3 trade config plus the active deterministic Phase 4 scheduling and Phase 5 inventory configs.</t>
+          <t xml:space="preserve">Revenue, Monte Carlo, and UI remain later-phase work. Trade_Inventory_FutureHooks now wires the active deterministic Phase 3 trade config plus the active deterministic Phase 4 scheduling, Phase 5 inventory, and Phase 6 financial configs.</t>
         </is>
       </c>
     </row>
@@ -250,12 +250,12 @@
       </c>
       <c r="B7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml / generated_phase2_scenario.toml, generated_phase3_parameters.toml / generated_phase3_scenario.toml, generated_phase4_parameters.toml / generated_phase4_scenario.toml, and generated_phase5_parameters.toml / generated_phase5_scenario.toml.</t>
+          <t xml:space="preserve">The importer generates machine-readable CSV artifacts plus generated_phase2_parameters.toml / generated_phase2_scenario.toml, generated_phase3_parameters.toml / generated_phase3_scenario.toml, generated_phase4_parameters.toml / generated_phase4_scenario.toml, generated_phase5_parameters.toml / generated_phase5_scenario.toml, and generated_phase6_parameters.toml / generated_phase6_scenario.toml.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode; dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2; active deterministic trade parameters from Trade_Inventory_FutureHooks for Phase 3; and active deterministic Phase 4 scheduling plus Phase 5 inventory controls from Trade_Inventory_FutureHooks together with the scenario-default Product_Parameters, Yield_Assumptions, and SS_Assumptions rows.</t>
+          <t xml:space="preserve">Current wiring consumes: Scenario_Controls.demand_basis plus Treatment_Duration_Assumptions for Phase 1 starts-based mode; dose_basis_default, module-specific dosing values, module FG mg per unit, module FG vialing rule, global yields, DS quantity per DP unit default, DS overage default, SS ratio, and co_pack_mode for Phase 2; active deterministic trade parameters from Trade_Inventory_FutureHooks for Phase 3; active deterministic Phase 4 scheduling plus Phase 5 inventory controls from Trade_Inventory_FutureHooks together with the scenario-default Product_Parameters, Yield_Assumptions, and SS_Assumptions rows; and active deterministic Phase 6 financial assumptions plus editable geography-bucketed Sub-Layer 1 -&gt; Sub-Layer 2 shipping/cold-chain cost parameters from Trade_Inventory_FutureHooks together with the scenario-default Product_Parameters, Yield_Assumptions, and SS_Assumptions rows.</t>
         </is>
       </c>
     </row>
@@ -272,7 +272,7 @@
       </c>
       <c r="C8" t="inlineStr" s="8">
         <is>
-          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic. Trade_Inventory_FutureHooks still carries a historical name, but it now also feeds the active deterministic Phase 3 trade config plus the active Phase 4 scheduling and Phase 5 inventory config bridges.</t>
+          <t xml:space="preserve">CML_Prevalent_Assumptions remains a dedicated artifact sheet. Populate approved pool, timing, and exhaustion metadata here without treating CML like AML/MDS segment mix logic. Trade_Inventory_FutureHooks still carries a historical name, but it now also feeds the active deterministic Phase 3 trade config plus the active Phase 4 scheduling, Phase 5 inventory, and Phase 6 financial config bridges.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BV21"/>
+  <dimension ref="A1:CN21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1217,6 +1217,20 @@
     <col min="71" max="71" width="18" customWidth="1"/>
     <col min="72" max="72" width="12" customWidth="1"/>
     <col min="73" max="73" width="72" customWidth="1"/>
+    <col min="74" max="74" width="18" customWidth="1"/>
+    <col min="75" max="75" width="18" customWidth="1"/>
+    <col min="76" max="76" width="18" customWidth="1"/>
+    <col min="77" max="77" width="20" customWidth="1"/>
+    <col min="78" max="78" width="18" customWidth="1"/>
+    <col min="79" max="79" width="18" customWidth="1"/>
+    <col min="80" max="80" width="18" customWidth="1"/>
+    <col min="81" max="81" width="18" customWidth="1"/>
+    <col min="82" max="82" width="18" customWidth="1"/>
+    <col min="83" max="83" width="18" customWidth="1"/>
+    <col min="84" max="84" width="18" customWidth="1"/>
+    <col min="85" max="85" width="20" customWidth="1"/>
+    <col min="86" max="86" width="18" customWidth="1"/>
+    <col min="87" max="87" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1588,6 +1602,96 @@
       <c r="BV1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_standard_cost_basis_unit</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ds_standard_cost_per_mg</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">dp_conversion_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">fg_packaging_labeling_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ss_standard_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">annual_inventory_carry_rate</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">monthly_inventory_carry_rate</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">expired_inventory_writeoff_rate</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">expired_inventory_salvage_rate</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">value_unmatched_fg_at_fg_standard_cost</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">include_trade_node_fg_value</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">use_matched_administrable_fg_value</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">phase6_enforce_unique_output_keys</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">phase6_reconciliation_tolerance_value</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">us_fg_sub1_to_sub2_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">eu_fg_sub1_to_sub2_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">us_ss_sub1_to_sub2_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">eu_ss_sub1_to_sub2_cost_per_unit</t>
         </is>
       </c>
     </row>
@@ -1827,8 +1931,72 @@
       </c>
       <c r="BV2" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Active deterministic defaults for Phase 3, Phase 4, and Phase 5. Phase 5 shelf life and excess-cover values are revised placeholder baseline assumptions; edit here instead of hand-editing phase3_trade_layer.toml, phase4_production_schedule.toml, or phase5_inventory_layer.toml.</t>
-        </is>
+          <t xml:space="preserve">Active deterministic defaults for Phase 3, Phase 4, Phase 5, and Phase 6. Phase 5 shelf life/excess-cover and Phase 6 standard-cost placeholders are revised baseline assumptions; edit here instead of hand-editing phase3_trade_layer.toml, phase4_production_schedule.toml, phase5_inventory_layer.toml, or phase6_financial_layer.toml.</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">mg</t>
+        </is>
+      </c>
+      <c r="BX2" s="2">
+        <v>0.002</v>
+      </c>
+      <c r="BY2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="BZ2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="CA2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="CB2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="CC2" s="2">
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="CD2" s="2">
+        <v>1</v>
+      </c>
+      <c r="CE2" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="CJ2" s="2">
+        <v>1e-06</v>
+      </c>
+      <c r="CK2" s="2">
+        <v>25</v>
+      </c>
+      <c r="CL2" s="2">
+        <v>57.5</v>
+      </c>
+      <c r="CM2" s="2">
+        <v>25</v>
+      </c>
+      <c r="CN2" s="2">
+        <v>57.5</v>
       </c>
     </row>
     <row r="3">
@@ -1934,6 +2102,24 @@
           <t xml:space="preserve">Approved/sample US site activation defaults for the deterministic Phase 3 trade layer.</t>
         </is>
       </c>
+      <c r="BW3" s="2"/>
+      <c r="BX3" s="2"/>
+      <c r="BY3" s="2"/>
+      <c r="BZ3" s="2"/>
+      <c r="CA3" s="2"/>
+      <c r="CB3" s="2"/>
+      <c r="CC3" s="2"/>
+      <c r="CD3" s="2"/>
+      <c r="CE3" s="2"/>
+      <c r="CF3" s="2"/>
+      <c r="CG3" s="2"/>
+      <c r="CH3" s="2"/>
+      <c r="CI3" s="2"/>
+      <c r="CJ3" s="2"/>
+      <c r="CK3" s="2"/>
+      <c r="CL3" s="2"/>
+      <c r="CM3" s="2"/>
+      <c r="CN3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -2038,6 +2224,24 @@
           <t xml:space="preserve">Approved/sample EU site activation defaults for the deterministic Phase 3 trade layer.</t>
         </is>
       </c>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
+      <c r="BY4" s="2"/>
+      <c r="BZ4" s="2"/>
+      <c r="CA4" s="2"/>
+      <c r="CB4" s="2"/>
+      <c r="CC4" s="2"/>
+      <c r="CD4" s="2"/>
+      <c r="CE4" s="2"/>
+      <c r="CF4" s="2"/>
+      <c r="CG4" s="2"/>
+      <c r="CH4" s="2"/>
+      <c r="CI4" s="2"/>
+      <c r="CJ4" s="2"/>
+      <c r="CK4" s="2"/>
+      <c r="CL4" s="2"/>
+      <c r="CM4" s="2"/>
+      <c r="CN4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -2138,6 +2342,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2"/>
+      <c r="BY5" s="2"/>
+      <c r="BZ5" s="2"/>
+      <c r="CA5" s="2"/>
+      <c r="CB5" s="2"/>
+      <c r="CC5" s="2"/>
+      <c r="CD5" s="2"/>
+      <c r="CE5" s="2"/>
+      <c r="CF5" s="2"/>
+      <c r="CG5" s="2"/>
+      <c r="CH5" s="2"/>
+      <c r="CI5" s="2"/>
+      <c r="CJ5" s="2"/>
+      <c r="CK5" s="2"/>
+      <c r="CL5" s="2"/>
+      <c r="CM5" s="2"/>
+      <c r="CN5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="3">
@@ -2238,6 +2460,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2"/>
+      <c r="BY6" s="2"/>
+      <c r="BZ6" s="2"/>
+      <c r="CA6" s="2"/>
+      <c r="CB6" s="2"/>
+      <c r="CC6" s="2"/>
+      <c r="CD6" s="2"/>
+      <c r="CE6" s="2"/>
+      <c r="CF6" s="2"/>
+      <c r="CG6" s="2"/>
+      <c r="CH6" s="2"/>
+      <c r="CI6" s="2"/>
+      <c r="CJ6" s="2"/>
+      <c r="CK6" s="2"/>
+      <c r="CL6" s="2"/>
+      <c r="CM6" s="2"/>
+      <c r="CN6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="3">
@@ -2338,6 +2578,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2"/>
+      <c r="BY7" s="2"/>
+      <c r="BZ7" s="2"/>
+      <c r="CA7" s="2"/>
+      <c r="CB7" s="2"/>
+      <c r="CC7" s="2"/>
+      <c r="CD7" s="2"/>
+      <c r="CE7" s="2"/>
+      <c r="CF7" s="2"/>
+      <c r="CG7" s="2"/>
+      <c r="CH7" s="2"/>
+      <c r="CI7" s="2"/>
+      <c r="CJ7" s="2"/>
+      <c r="CK7" s="2"/>
+      <c r="CL7" s="2"/>
+      <c r="CM7" s="2"/>
+      <c r="CN7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="3">
@@ -2438,6 +2696,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW8" s="2"/>
+      <c r="BX8" s="2"/>
+      <c r="BY8" s="2"/>
+      <c r="BZ8" s="2"/>
+      <c r="CA8" s="2"/>
+      <c r="CB8" s="2"/>
+      <c r="CC8" s="2"/>
+      <c r="CD8" s="2"/>
+      <c r="CE8" s="2"/>
+      <c r="CF8" s="2"/>
+      <c r="CG8" s="2"/>
+      <c r="CH8" s="2"/>
+      <c r="CI8" s="2"/>
+      <c r="CJ8" s="2"/>
+      <c r="CK8" s="2"/>
+      <c r="CL8" s="2"/>
+      <c r="CM8" s="2"/>
+      <c r="CN8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="3">
@@ -2538,6 +2814,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW9" s="2"/>
+      <c r="BX9" s="2"/>
+      <c r="BY9" s="2"/>
+      <c r="BZ9" s="2"/>
+      <c r="CA9" s="2"/>
+      <c r="CB9" s="2"/>
+      <c r="CC9" s="2"/>
+      <c r="CD9" s="2"/>
+      <c r="CE9" s="2"/>
+      <c r="CF9" s="2"/>
+      <c r="CG9" s="2"/>
+      <c r="CH9" s="2"/>
+      <c r="CI9" s="2"/>
+      <c r="CJ9" s="2"/>
+      <c r="CK9" s="2"/>
+      <c r="CL9" s="2"/>
+      <c r="CM9" s="2"/>
+      <c r="CN9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="3">
@@ -2638,6 +2932,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW10" s="2"/>
+      <c r="BX10" s="2"/>
+      <c r="BY10" s="2"/>
+      <c r="BZ10" s="2"/>
+      <c r="CA10" s="2"/>
+      <c r="CB10" s="2"/>
+      <c r="CC10" s="2"/>
+      <c r="CD10" s="2"/>
+      <c r="CE10" s="2"/>
+      <c r="CF10" s="2"/>
+      <c r="CG10" s="2"/>
+      <c r="CH10" s="2"/>
+      <c r="CI10" s="2"/>
+      <c r="CJ10" s="2"/>
+      <c r="CK10" s="2"/>
+      <c r="CL10" s="2"/>
+      <c r="CM10" s="2"/>
+      <c r="CN10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="3">
@@ -2738,6 +3050,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW11" s="2"/>
+      <c r="BX11" s="2"/>
+      <c r="BY11" s="2"/>
+      <c r="BZ11" s="2"/>
+      <c r="CA11" s="2"/>
+      <c r="CB11" s="2"/>
+      <c r="CC11" s="2"/>
+      <c r="CD11" s="2"/>
+      <c r="CE11" s="2"/>
+      <c r="CF11" s="2"/>
+      <c r="CG11" s="2"/>
+      <c r="CH11" s="2"/>
+      <c r="CI11" s="2"/>
+      <c r="CJ11" s="2"/>
+      <c r="CK11" s="2"/>
+      <c r="CL11" s="2"/>
+      <c r="CM11" s="2"/>
+      <c r="CN11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="3">
@@ -2838,6 +3168,24 @@
           <t xml:space="preserve">Approved/sample launch event.</t>
         </is>
       </c>
+      <c r="BW12" s="2"/>
+      <c r="BX12" s="2"/>
+      <c r="BY12" s="2"/>
+      <c r="BZ12" s="2"/>
+      <c r="CA12" s="2"/>
+      <c r="CB12" s="2"/>
+      <c r="CC12" s="2"/>
+      <c r="CD12" s="2"/>
+      <c r="CE12" s="2"/>
+      <c r="CF12" s="2"/>
+      <c r="CG12" s="2"/>
+      <c r="CH12" s="2"/>
+      <c r="CI12" s="2"/>
+      <c r="CJ12" s="2"/>
+      <c r="CK12" s="2"/>
+      <c r="CL12" s="2"/>
+      <c r="CM12" s="2"/>
+      <c r="CN12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -2914,6 +3262,24 @@
       <c r="BT13" s="2"/>
       <c r="BU13" s="2"/>
       <c r="BV13" s="9"/>
+      <c r="BW13" s="2"/>
+      <c r="BX13" s="2"/>
+      <c r="BY13" s="2"/>
+      <c r="BZ13" s="2"/>
+      <c r="CA13" s="2"/>
+      <c r="CB13" s="2"/>
+      <c r="CC13" s="2"/>
+      <c r="CD13" s="2"/>
+      <c r="CE13" s="2"/>
+      <c r="CF13" s="2"/>
+      <c r="CG13" s="2"/>
+      <c r="CH13" s="2"/>
+      <c r="CI13" s="2"/>
+      <c r="CJ13" s="2"/>
+      <c r="CK13" s="2"/>
+      <c r="CL13" s="2"/>
+      <c r="CM13" s="2"/>
+      <c r="CN13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -2990,6 +3356,24 @@
       <c r="BT14" s="2"/>
       <c r="BU14" s="2"/>
       <c r="BV14" s="9"/>
+      <c r="BW14" s="2"/>
+      <c r="BX14" s="2"/>
+      <c r="BY14" s="2"/>
+      <c r="BZ14" s="2"/>
+      <c r="CA14" s="2"/>
+      <c r="CB14" s="2"/>
+      <c r="CC14" s="2"/>
+      <c r="CD14" s="2"/>
+      <c r="CE14" s="2"/>
+      <c r="CF14" s="2"/>
+      <c r="CG14" s="2"/>
+      <c r="CH14" s="2"/>
+      <c r="CI14" s="2"/>
+      <c r="CJ14" s="2"/>
+      <c r="CK14" s="2"/>
+      <c r="CL14" s="2"/>
+      <c r="CM14" s="2"/>
+      <c r="CN14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -3066,6 +3450,24 @@
       <c r="BT15" s="2"/>
       <c r="BU15" s="2"/>
       <c r="BV15" s="9"/>
+      <c r="BW15" s="2"/>
+      <c r="BX15" s="2"/>
+      <c r="BY15" s="2"/>
+      <c r="BZ15" s="2"/>
+      <c r="CA15" s="2"/>
+      <c r="CB15" s="2"/>
+      <c r="CC15" s="2"/>
+      <c r="CD15" s="2"/>
+      <c r="CE15" s="2"/>
+      <c r="CF15" s="2"/>
+      <c r="CG15" s="2"/>
+      <c r="CH15" s="2"/>
+      <c r="CI15" s="2"/>
+      <c r="CJ15" s="2"/>
+      <c r="CK15" s="2"/>
+      <c r="CL15" s="2"/>
+      <c r="CM15" s="2"/>
+      <c r="CN15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -3142,6 +3544,24 @@
       <c r="BT16" s="2"/>
       <c r="BU16" s="2"/>
       <c r="BV16" s="9"/>
+      <c r="BW16" s="2"/>
+      <c r="BX16" s="2"/>
+      <c r="BY16" s="2"/>
+      <c r="BZ16" s="2"/>
+      <c r="CA16" s="2"/>
+      <c r="CB16" s="2"/>
+      <c r="CC16" s="2"/>
+      <c r="CD16" s="2"/>
+      <c r="CE16" s="2"/>
+      <c r="CF16" s="2"/>
+      <c r="CG16" s="2"/>
+      <c r="CH16" s="2"/>
+      <c r="CI16" s="2"/>
+      <c r="CJ16" s="2"/>
+      <c r="CK16" s="2"/>
+      <c r="CL16" s="2"/>
+      <c r="CM16" s="2"/>
+      <c r="CN16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -3218,6 +3638,24 @@
       <c r="BT17" s="2"/>
       <c r="BU17" s="2"/>
       <c r="BV17" s="9"/>
+      <c r="BW17" s="2"/>
+      <c r="BX17" s="2"/>
+      <c r="BY17" s="2"/>
+      <c r="BZ17" s="2"/>
+      <c r="CA17" s="2"/>
+      <c r="CB17" s="2"/>
+      <c r="CC17" s="2"/>
+      <c r="CD17" s="2"/>
+      <c r="CE17" s="2"/>
+      <c r="CF17" s="2"/>
+      <c r="CG17" s="2"/>
+      <c r="CH17" s="2"/>
+      <c r="CI17" s="2"/>
+      <c r="CJ17" s="2"/>
+      <c r="CK17" s="2"/>
+      <c r="CL17" s="2"/>
+      <c r="CM17" s="2"/>
+      <c r="CN17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -3294,6 +3732,24 @@
       <c r="BT18" s="2"/>
       <c r="BU18" s="2"/>
       <c r="BV18" s="9"/>
+      <c r="BW18" s="2"/>
+      <c r="BX18" s="2"/>
+      <c r="BY18" s="2"/>
+      <c r="BZ18" s="2"/>
+      <c r="CA18" s="2"/>
+      <c r="CB18" s="2"/>
+      <c r="CC18" s="2"/>
+      <c r="CD18" s="2"/>
+      <c r="CE18" s="2"/>
+      <c r="CF18" s="2"/>
+      <c r="CG18" s="2"/>
+      <c r="CH18" s="2"/>
+      <c r="CI18" s="2"/>
+      <c r="CJ18" s="2"/>
+      <c r="CK18" s="2"/>
+      <c r="CL18" s="2"/>
+      <c r="CM18" s="2"/>
+      <c r="CN18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -3370,6 +3826,24 @@
       <c r="BT19" s="2"/>
       <c r="BU19" s="2"/>
       <c r="BV19" s="9"/>
+      <c r="BW19" s="2"/>
+      <c r="BX19" s="2"/>
+      <c r="BY19" s="2"/>
+      <c r="BZ19" s="2"/>
+      <c r="CA19" s="2"/>
+      <c r="CB19" s="2"/>
+      <c r="CC19" s="2"/>
+      <c r="CD19" s="2"/>
+      <c r="CE19" s="2"/>
+      <c r="CF19" s="2"/>
+      <c r="CG19" s="2"/>
+      <c r="CH19" s="2"/>
+      <c r="CI19" s="2"/>
+      <c r="CJ19" s="2"/>
+      <c r="CK19" s="2"/>
+      <c r="CL19" s="2"/>
+      <c r="CM19" s="2"/>
+      <c r="CN19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -3446,6 +3920,24 @@
       <c r="BT20" s="2"/>
       <c r="BU20" s="2"/>
       <c r="BV20" s="9"/>
+      <c r="BW20" s="2"/>
+      <c r="BX20" s="2"/>
+      <c r="BY20" s="2"/>
+      <c r="BZ20" s="2"/>
+      <c r="CA20" s="2"/>
+      <c r="CB20" s="2"/>
+      <c r="CC20" s="2"/>
+      <c r="CD20" s="2"/>
+      <c r="CE20" s="2"/>
+      <c r="CF20" s="2"/>
+      <c r="CG20" s="2"/>
+      <c r="CH20" s="2"/>
+      <c r="CI20" s="2"/>
+      <c r="CJ20" s="2"/>
+      <c r="CK20" s="2"/>
+      <c r="CL20" s="2"/>
+      <c r="CM20" s="2"/>
+      <c r="CN20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -3522,10 +4014,28 @@
       <c r="BT21" s="2"/>
       <c r="BU21" s="2"/>
       <c r="BV21" s="9"/>
+      <c r="BW21" s="2"/>
+      <c r="BX21" s="2"/>
+      <c r="BY21" s="2"/>
+      <c r="BZ21" s="2"/>
+      <c r="CA21" s="2"/>
+      <c r="CB21" s="2"/>
+      <c r="CC21" s="2"/>
+      <c r="CD21" s="2"/>
+      <c r="CE21" s="2"/>
+      <c r="CF21" s="2"/>
+      <c r="CG21" s="2"/>
+      <c r="CH21" s="2"/>
+      <c r="CI21" s="2"/>
+      <c r="CJ21" s="2"/>
+      <c r="CK21" s="2"/>
+      <c r="CL21" s="2"/>
+      <c r="CM21" s="2"/>
+      <c r="CN21" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BV1"/>
-  <dataValidations count="6">
+  <autoFilter ref="A1:CJ1"/>
+  <dataValidations count="7">
     <dataValidation type="list" sqref="B2:B21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$O$2:$O$4</formula1>
     </dataValidation>
@@ -3543,6 +4053,9 @@
     </dataValidation>
     <dataValidation type="list" sqref="BU2:BU21" showErrorMessage="1" allowBlank="1">
       <formula1>Lookup_Lists!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="CF2:CI21" showErrorMessage="1" allowBlank="1">
+      <formula1>Lookup_Lists!$F$2:$F$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
